--- a/samples/mapping/invoice/page-breaks/invoice.xlsx
+++ b/samples/mapping/invoice/page-breaks/invoice.xlsx
@@ -993,7 +993,6 @@
         <x:v>12345.6</x:v>
       </x:c>
       <x:c r="F9" s="30">
-        <x:f>D9*E9</x:f>
         <x:v>30864</x:v>
       </x:c>
     </x:row>
@@ -1032,7 +1031,6 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="F11" s="30">
-        <x:f>D11*E11</x:f>
         <x:v>2000</x:v>
       </x:c>
     </x:row>
@@ -1481,7 +1479,6 @@
         <x:v>-500</x:v>
       </x:c>
       <x:c r="F47" s="30">
-        <x:f>D47*E47</x:f>
         <x:v>-500</x:v>
       </x:c>
     </x:row>
